--- a/data/G2025_resultados_diputados_nacionales.xlsx
+++ b/data/G2025_resultados_diputados_nacionales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas.bustos\Documents\personal\estacion-r\Mapas en accion\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas.bustos\Documents\personal\estacion-r\mapas_en_accion\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94086BA-34FE-42D8-A881-A6617001439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DA387A-D1A2-4B36-8466-B74A15983EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -150,8 +150,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,7 +467,7 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>36.6</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -480,7 +481,7 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>31.7</v>
+        <v>33.630000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -494,7 +495,7 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>46.8</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -508,7 +509,7 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -522,7 +523,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>36.1</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -536,7 +537,7 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>25.2</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -550,7 +551,7 @@
         <v>16</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -564,7 +565,7 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>52.2</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -578,7 +579,7 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>35.869999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -592,7 +593,7 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <v>33.799999999999997</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -606,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -620,7 +621,7 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>43.27</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -634,7 +635,7 @@
         <v>16</v>
       </c>
       <c r="D14">
-        <v>46.9</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -648,7 +649,7 @@
         <v>16</v>
       </c>
       <c r="D15">
-        <v>36.700000000000003</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -662,7 +663,7 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -676,7 +677,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>33</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -690,7 +691,7 @@
         <v>16</v>
       </c>
       <c r="D18">
-        <v>40.799999999999997</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -703,8 +704,8 @@
       <c r="C19" t="s">
         <v>16</v>
       </c>
-      <c r="D19">
-        <v>33</v>
+      <c r="D19" s="1">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -718,7 +719,7 @@
         <v>16</v>
       </c>
       <c r="D20">
-        <v>33</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -732,7 +733,7 @@
         <v>16</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -746,7 +747,7 @@
         <v>16</v>
       </c>
       <c r="D22">
-        <v>38.9</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -760,7 +761,7 @@
         <v>16</v>
       </c>
       <c r="D23">
-        <v>33</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -774,7 +775,7 @@
         <v>16</v>
       </c>
       <c r="D24">
-        <v>33</v>
+        <v>38.549999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -788,10 +789,13 @@
         <v>16</v>
       </c>
       <c r="D25">
-        <v>22.2</v>
+        <v>35.119999999999997</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J2:K25">
+    <sortCondition ref="J2:J25"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>